--- a/test_samples/PANCARAN/sample1_ref.xlsx
+++ b/test_samples/PANCARAN/sample1_ref.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\LC\供應商帳單\PANCARAN____________________要確認材積,先用NA!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jeffrey.hu\Desktop\印尼供應商帳單\PANCARAN_____________OK\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF2719CB-1AAB-44C0-83F4-44F941D6469D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA98924C-7D43-42D4-A435-7A13DAA04D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17820" yWindow="4860" windowWidth="20130" windowHeight="15240" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
+    <workbookView xWindow="8145" yWindow="7665" windowWidth="28800" windowHeight="12855" tabRatio="819" xr2:uid="{B2E6A21A-966E-4572-9141-AA1879003F42}"/>
   </bookViews>
   <sheets>
     <sheet name="DWIHARTA" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="32">
   <si>
     <t>INVOICE DATE
 發票日期</t>
@@ -152,6 +152,35 @@
     <t>PYI-2026.08.151/152/154/161/162/163/164/166/167
 /171/175/176/178/180/181/182</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Shipper
+出貨方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CIANJUR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GD. TUNGYA , GD.GLT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>N/A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LCL - 13x40HC LCL - 2xBOXCDDLCL -
+1xBOXFUSO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXPJK26080029</t>
   </si>
 </sst>
 </file>
@@ -243,7 +272,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -579,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF1381F-552A-4924-9A7A-4C0080F73CE6}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.375" customWidth="1"/>
@@ -587,19 +616,20 @@
     <col min="3" max="3" width="29.5" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.875" customWidth="1"/>
-    <col min="7" max="7" width="29.25" customWidth="1"/>
-    <col min="8" max="9" width="13.75" customWidth="1"/>
-    <col min="10" max="10" width="20.5" customWidth="1"/>
-    <col min="11" max="11" width="20" customWidth="1"/>
-    <col min="12" max="12" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.375" customWidth="1"/>
-    <col min="15" max="15" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="17.875" customWidth="1"/>
+    <col min="8" max="8" width="29.25" customWidth="1"/>
+    <col min="9" max="10" width="13.75" customWidth="1"/>
+    <col min="11" max="11" width="20.5" customWidth="1"/>
+    <col min="12" max="12" width="20" customWidth="1"/>
+    <col min="13" max="13" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.375" customWidth="1"/>
+    <col min="16" max="16" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -619,37 +649,43 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="247.5" x14ac:dyDescent="0.25">
+      <c r="R1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>46269</v>
       </c>
@@ -668,11 +704,9 @@
       <c r="F2" s="4">
         <v>5950000</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="4"/>
+      <c r="H2" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
       </c>
       <c r="I2" t="s">
         <v>16</v>
@@ -681,25 +715,31 @@
         <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
         <v>16</v>
       </c>
       <c r="M2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" ht="247.5" x14ac:dyDescent="0.25">
+      <c r="R2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>46269</v>
       </c>
@@ -718,11 +758,9 @@
       <c r="F3" s="4">
         <v>4165000</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="4"/>
+      <c r="H3" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
@@ -731,25 +769,31 @@
         <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="L3" t="s">
         <v>16</v>
       </c>
       <c r="M3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N3" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="247.5" x14ac:dyDescent="0.25">
+      <c r="R3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>46269</v>
       </c>
@@ -768,11 +812,9 @@
       <c r="F4" s="4">
         <v>75660000</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -781,61 +823,62 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="L4" t="s">
         <v>16</v>
       </c>
       <c r="M4" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N4" t="s">
-        <v>16</v>
-      </c>
-      <c r="O4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="H5" s="7"/>
       <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="7"/>
+    </row>
+    <row r="6" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="H6" s="7"/>
       <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
-      <c r="H7" s="7"/>
       <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J7" s="7"/>
+    </row>
+    <row r="8" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
-      <c r="H8" s="7"/>
       <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J8" s="7"/>
+    </row>
+    <row r="9" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
-      <c r="H9" s="7"/>
       <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:18" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
-      <c r="H10" s="7"/>
       <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="Q12" s="1"/>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
